--- a/data/AMS Planejamento.xlsx
+++ b/data/AMS Planejamento.xlsx
@@ -80,9 +80,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -120,7 +120,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -226,7 +226,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -368,7 +368,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -378,16 +378,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G21"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="5.83203125"/>
-    <col min="2" max="2" customWidth="1" width="12.83203125"/>
-    <col min="3" max="3" customWidth="1" width="72.83203125"/>
-    <col min="4" max="4" customWidth="1" width="55.83203125"/>
-    <col min="5" max="5" customWidth="1" width="16.83203125"/>
-    <col min="6" max="6" customWidth="1" width="14.83203125"/>
-    <col min="7" max="7" customWidth="1" width="58.83203125"/>
+    <col min="1" max="1" customWidth="1" width="5.796875"/>
+    <col min="2" max="2" customWidth="1" width="12.796875"/>
+    <col min="3" max="3" customWidth="1" width="72.796875"/>
+    <col min="4" max="4" customWidth="1" width="55.796875"/>
+    <col min="5" max="5" customWidth="1" width="16.796875"/>
+    <col min="6" max="6" customWidth="1" width="14.796875"/>
+    <col min="7" max="7" customWidth="1" width="58.796875"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.6" customHeight="1">
       <c r="A1" t="str">
         <v>N</v>
       </c>
@@ -410,7 +410,7 @@
         <v>Observações</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.6" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -433,7 +433,7 @@
         <v>Apresentação da ementa, metodologia, avaliação e projeto integrador.</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.6" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -456,7 +456,7 @@
         <v>Montagem de equipes, definição do problema, imersão, ideação e prototipação.</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.6" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -479,7 +479,7 @@
         <v>Módulo 1 — Fundamentos e ecossistema de dados.</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.6" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -502,7 +502,7 @@
         <v>Módulo 1 — Fundamentos e ecossistema de dados.</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.6" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -525,7 +525,7 @@
         <v>Módulo 1 — Fundamentos e ecossistema de dados.</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.6" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -548,15 +548,16 @@
         <v>Módulo 2 — Desenho de estudos e aprendizado de máquina clássico.</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="31.2" customHeight="1" xml:space="preserve">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>46283</v>
       </c>
-      <c r="C8" t="str">
-        <v>Aula 5: Avaliação de desempenho e validação</v>
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aula 5: Avaliação de desempenho e validação_x000d_
+Aula 6: Aprendizado supervisionado e não supervisionado clássico</v>
       </c>
       <c r="D8" t="str">
         <v>JAMES et al. (2023); COLLINS et al. (2024)</v>
@@ -571,7 +572,7 @@
         <v>Módulo 2 — Desenho de estudos e aprendizado de máquina clássico.</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.6" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -579,13 +580,10 @@
         <v>46290</v>
       </c>
       <c r="C9" t="str">
-        <v>Aula 6: Aprendizado supervisionado e não supervisionado clássico</v>
-      </c>
-      <c r="D9" t="str">
-        <v>JAMES et al. (2023)</v>
+        <v>Apresentação de artigo 1</v>
       </c>
       <c r="E9" t="str">
-        <v>aula</v>
+        <v>apresentacao</v>
       </c>
       <c r="F9" t="str">
         <v>planned</v>
@@ -594,7 +592,7 @@
         <v>Módulo 2 — Desenho de estudos e aprendizado de máquina clássico.</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.6" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -617,7 +615,7 @@
         <v>Módulo 3 — Aprendizado profundo e NLP.</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.6" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -640,15 +638,16 @@
         <v>Módulo 3 — Aprendizado profundo e NLP.</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="34.05" customHeight="1" xml:space="preserve">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>46311</v>
       </c>
-      <c r="C12" t="str">
-        <v>Aulas 9 e 10: Processamento de linguagem natural biomédico; modelos de linguagem e multimodalidade</v>
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aula 9: Processamento de linguagem natural biomédico; _x000d_
+Aula 10: Modelos de linguagem e multimodalidade</v>
       </c>
       <c r="D12" t="str">
         <v>WORLD HEALTH ORGANIZATION (2024)</v>
@@ -663,15 +662,16 @@
         <v>Módulo 3 — Aprendizado profundo e NLP.</v>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="34.05" customHeight="1" xml:space="preserve">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>46318</v>
       </c>
-      <c r="C13" t="str">
-        <v>Aulas 11 e 12: Análise de sobrevivência, predição de risco, inferência causal e evidência de mundo real</v>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aula 11: Análise de sobrevivência, predição de risco_x000d_
+Aula 12: Inferência causal e evidência de mundo real</v>
       </c>
       <c r="D13" t="str">
         <v>WANG; LI; REDDY (2019); HERNÁN; ROBINS (2020)</v>
@@ -686,7 +686,7 @@
         <v>Módulo 4 — Sobrevivência, inferência causal e decisão.</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.6" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -694,13 +694,10 @@
         <v>46325</v>
       </c>
       <c r="C14" t="str">
-        <v>Aula 13: Sistemas de apoio à decisão clínica e implementação</v>
-      </c>
-      <c r="D14" t="str">
-        <v>BERNER (2007)</v>
+        <v>Semana de extensão (SEMEXT)</v>
       </c>
       <c r="E14" t="str">
-        <v>aula</v>
+        <v>atividade</v>
       </c>
       <c r="F14" t="str">
         <v>planned</v>
@@ -709,18 +706,20 @@
         <v>Módulo 4 — Sobrevivência, inferência causal e decisão.</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="46.79999999999999" customHeight="1" xml:space="preserve">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>46332</v>
       </c>
-      <c r="C15" t="str">
-        <v>Aula 14: Explicabilidade, equidade e privacidade</v>
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Aula 13: Sistemas de apoio à decisão clínica e implementação_x000d_
+Aula 14: Explicabilidade, equidade e privacidade_x000d_
+Aula 15: Regulação, relato científico e MLOps</v>
       </c>
       <c r="D15" t="str">
-        <v>WORLD HEALTH ORGANIZATION (2021)</v>
+        <v>BERNER (2007); WORLD HEALTH ORGANIZATION (2021); ANVISA (2022); FDA (2025); COLLINS et al. (2024)</v>
       </c>
       <c r="E15" t="str">
         <v>aula</v>
@@ -732,7 +731,7 @@
         <v>Módulo 5 — Ética, regulação e prática profissional.</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.6" customHeight="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -740,13 +739,10 @@
         <v>46339</v>
       </c>
       <c r="C16" t="str">
-        <v>Aula 15: Regulação, relato científico e MLOps</v>
-      </c>
-      <c r="D16" t="str">
-        <v>ANVISA (2022); FDA (2025); COLLINS et al. (2024)</v>
+        <v>Apresentação de artigo 2</v>
       </c>
       <c r="E16" t="str">
-        <v>aula</v>
+        <v>apresentacao</v>
       </c>
       <c r="F16" t="str">
         <v>planned</v>
@@ -755,7 +751,7 @@
         <v>Módulo 5 — Ética, regulação e prática profissional.</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.6" customHeight="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -775,7 +771,7 @@
         <v>Não haverá aula.</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.6" customHeight="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -798,7 +794,7 @@
         <v>Módulo 5 — Ética, regulação e prática profissional.</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.6" customHeight="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -818,8 +814,8 @@
         <v>Apresentação e discussão dos miniprojetos desenvolvidos pelas equipes.</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
+    <row r="20" ht="15.6" customHeight="1"/>
+    <row r="21" ht="15.6" customHeight="1">
       <c r="D21" t="str">
         <v/>
       </c>
